--- a/data/trans_camb/P36B08_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28,63</t>
+          <t>29,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,69</t>
+          <t>21,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24,8</t>
+          <t>25,1</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 13,16</t>
+          <t>4,58; 12,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 16,65</t>
+          <t>8,29; 16,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 32,05</t>
+          <t>25,54; 32,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 11,04</t>
+          <t>4,74; 11,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 10,09</t>
+          <t>3,02; 10,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,69; 24,34</t>
+          <t>19,36; 24,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,94</t>
+          <t>5,67; 10,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,53</t>
+          <t>6,11; 11,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,51; 27,01</t>
+          <t>23,02; 27,34</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 21,16</t>
+          <t>6,8; 20,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,93; 26,81</t>
+          <t>12,65; 27,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,39; 51,8</t>
+          <t>38,55; 53,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 15,57</t>
+          <t>6,31; 15,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 14,26</t>
+          <t>3,96; 14,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,85; 34,39</t>
+          <t>25,78; 35,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,08; 16,03</t>
+          <t>8,03; 16,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 16,92</t>
+          <t>8,71; 17,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,93; 40,11</t>
+          <t>32,53; 40,64</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,44</t>
+          <t>32,19</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,51</t>
+          <t>26,21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29,6</t>
+          <t>29,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 10,56</t>
+          <t>4,25; 10,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 10,65</t>
+          <t>4,07; 10,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,69; 35,39</t>
+          <t>29,41; 34,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,82</t>
+          <t>4,51; 11,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,46</t>
+          <t>2,49; 8,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,1; 29,5</t>
+          <t>23,89; 28,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 10,04</t>
+          <t>5,25; 9,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,86</t>
+          <t>4,38; 8,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,81; 31,54</t>
+          <t>27,56; 31,25</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,02; 17,7</t>
+          <t>6,66; 18,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 17,76</t>
+          <t>6,34; 17,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,64; 59,08</t>
+          <t>46,21; 58,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 16,0</t>
+          <t>6,26; 16,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 12,37</t>
+          <t>3,37; 12,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,41; 43,78</t>
+          <t>33,35; 42,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 15,57</t>
+          <t>7,92; 15,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 13,73</t>
+          <t>6,53; 13,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,55; 49,24</t>
+          <t>41,14; 48,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>30,67</t>
+          <t>30,5</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,69</t>
+          <t>25,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28,35</t>
+          <t>28,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 14,85</t>
+          <t>3,25; 14,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,3; 17,68</t>
+          <t>6,7; 17,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26,38; 35,04</t>
+          <t>26,22; 34,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,69; 20,06</t>
+          <t>8,61; 19,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 16,33</t>
+          <t>5,52; 16,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,54; 30,61</t>
+          <t>21,63; 30,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 15,79</t>
+          <t>7,34; 15,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,63; 15,34</t>
+          <t>7,97; 15,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,25; 31,62</t>
+          <t>25,35; 31,53</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,22; 23,58</t>
+          <t>4,63; 23,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,94; 27,66</t>
+          <t>9,6; 28,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,63; 56,43</t>
+          <t>37,11; 55,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,66; 29,5</t>
+          <t>11,81; 29,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,48; 24,09</t>
+          <t>7,38; 24,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,84; 45,49</t>
+          <t>29,17; 47,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 24,01</t>
+          <t>10,55; 23,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,74; 23,4</t>
+          <t>11,32; 23,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>35,68; 48,38</t>
+          <t>35,47; 47,91</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31,21</t>
+          <t>31,14</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,83</t>
+          <t>24,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>27,98</t>
+          <t>27,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,28</t>
+          <t>5,51; 10,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 11,3</t>
+          <t>6,84; 11,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,1; 33,29</t>
+          <t>29,15; 32,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,38</t>
+          <t>6,31; 10,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,35</t>
+          <t>4,22; 8,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,15; 26,46</t>
+          <t>23,09; 26,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 9,74</t>
+          <t>6,7; 9,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 9,32</t>
+          <t>6,14; 9,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,51; 29,39</t>
+          <t>26,69; 29,21</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,72; 16,58</t>
+          <t>8,62; 16,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,24</t>
+          <t>10,58; 18,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,91; 53,82</t>
+          <t>44,85; 53,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,58; 14,83</t>
+          <t>8,76; 14,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,82; 11,94</t>
+          <t>5,84; 11,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,87; 37,92</t>
+          <t>31,81; 37,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,65; 14,67</t>
+          <t>9,85; 15,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,99</t>
+          <t>9,02; 13,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>38,74; 44,34</t>
+          <t>39,04; 44,07</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P36B08_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P36B08_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
